--- a/zwt-finance-system/backend/app/assets/templates/TAX-INV-Template.xlsx
+++ b/zwt-finance-system/backend/app/assets/templates/TAX-INV-Template.xlsx
@@ -678,10 +678,12 @@
     </r>
   </si>
   <si>
-    <t>วันที่อัตราแลกเปลี่ยน</t>
+    <t>วันที่อัตรา
+แลกเปลี่ยน</t>
   </si>
   <si>
-    <t>อัตราแลกเปลี่ยน</t>
+    <t>อัตรา
+แลกเปลี่ยน</t>
   </si>
   <si>
     <r>
@@ -1647,9 +1649,16 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="8"/>
+      <b/>
+      <sz val="26"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Angsana New"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1657,19 +1666,6 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Leelawadee"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="26"/>
-      <color theme="1"/>
-      <name val="Angsana New"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1685,9 +1681,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="8"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
